--- a/project_documents/Project tracker.xlsx
+++ b/project_documents/Project tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gen_ai\final_capstone_project\project_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6DB14F-4DFC-49B6-A423-A5DDC5327F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DD4623-B09A-4801-B825-0FEC5482D932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="145">
   <si>
     <t>MediAssist AI Capstone Project Tracker</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Unit Testing</t>
   </si>
   <si>
-    <t>Unit Test Report</t>
-  </si>
-  <si>
     <t>Integration Testing</t>
   </si>
   <si>
@@ -292,12 +289,6 @@
     <t>Evaluation Report</t>
   </si>
   <si>
-    <t>Monitoring Dashboard</t>
-  </si>
-  <si>
-    <t>Security Layer</t>
-  </si>
-  <si>
     <t>Project Setup &amp; Planning</t>
   </si>
   <si>
@@ -415,43 +406,22 @@
     <t>Secure AI workflows</t>
   </si>
   <si>
-    <t>PHI masking, prompt protection</t>
-  </si>
-  <si>
     <t>Observability &amp; Logging</t>
   </si>
   <si>
     <t>Monitor workflows</t>
   </si>
   <si>
-    <t>Tracing and logs</t>
-  </si>
-  <si>
     <t>Validate modules</t>
   </si>
   <si>
-    <t>Test development</t>
-  </si>
-  <si>
     <t>Validate end-to-end workflows</t>
   </si>
   <si>
-    <t>System testing</t>
-  </si>
-  <si>
-    <t>Integration Report</t>
-  </si>
-  <si>
     <t>Performance Testing</t>
   </si>
   <si>
     <t>Measure scalability</t>
-  </si>
-  <si>
-    <t>Load testing</t>
-  </si>
-  <si>
-    <t>Performance Report</t>
   </si>
   <si>
     <t>Containerize solution</t>
@@ -652,11 +622,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,16 +856,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -1299,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>4</v>
@@ -1325,7 +1295,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>11</v>
@@ -1351,7 +1321,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>15</v>
@@ -1371,24 +1341,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="F4" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="18">
         <v>46186</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="18">
         <v>46190</v>
       </c>
     </row>
@@ -1397,24 +1367,24 @@
         <v>5</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="18">
         <v>46186</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <v>46190</v>
       </c>
     </row>
@@ -1423,24 +1393,24 @@
         <v>6</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>99</v>
-      </c>
       <c r="F6" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>46186</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>46190</v>
       </c>
     </row>
@@ -1452,21 +1422,21 @@
         <v>56</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>73</v>
-      </c>
       <c r="F7" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="18">
         <v>46186</v>
       </c>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <v>46190</v>
       </c>
     </row>
@@ -1475,24 +1445,24 @@
         <v>8</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <v>46190</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="18">
         <v>46192</v>
       </c>
     </row>
@@ -1504,10 +1474,10 @@
         <v>19</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>57</v>
@@ -1515,10 +1485,10 @@
       <c r="F9" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="18">
         <v>46190</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="18">
         <v>46192</v>
       </c>
     </row>
@@ -1530,21 +1500,21 @@
         <v>22</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="18">
         <v>46190</v>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="18">
         <v>46192</v>
       </c>
     </row>
@@ -1553,24 +1523,24 @@
         <v>11</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="18">
         <v>46190</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="18">
         <v>46192</v>
       </c>
     </row>
@@ -1579,24 +1549,24 @@
         <v>12</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="F12" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <v>46190</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <v>46192</v>
       </c>
     </row>
@@ -1608,17 +1578,23 @@
         <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+        <v>102</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="18">
+        <v>46193</v>
+      </c>
+      <c r="H13" s="18">
+        <v>46197</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="10">
@@ -1628,17 +1604,23 @@
         <v>59</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="F14" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="18">
+        <v>46193</v>
+      </c>
+      <c r="H14" s="18">
+        <v>46197</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="10">
@@ -1648,17 +1630,23 @@
         <v>60</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="F15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="18">
+        <v>46193</v>
+      </c>
+      <c r="H15" s="18">
+        <v>46197</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="10">
@@ -1668,17 +1656,23 @@
         <v>61</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="F16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="18">
+        <v>46193</v>
+      </c>
+      <c r="H16" s="18">
+        <v>46197</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="10">
@@ -1688,17 +1682,23 @@
         <v>62</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="F17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="18">
+        <v>46198</v>
+      </c>
+      <c r="H17" s="18">
+        <v>46203</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="10">
@@ -1708,77 +1708,101 @@
         <v>63</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="F18" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="18">
+        <v>46198</v>
+      </c>
+      <c r="H18" s="18">
+        <v>46203</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6">
         <v>19</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="E19" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="18">
+        <v>46203</v>
+      </c>
+      <c r="H19" s="18">
+        <v>46206</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="10">
         <v>20</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+        <v>115</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="18">
+        <v>46203</v>
+      </c>
+      <c r="H20" s="18">
+        <v>46206</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="10">
         <v>21</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="D21" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="18">
+        <v>46203</v>
+      </c>
+      <c r="H21" s="18">
+        <v>46206</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="10">
@@ -1788,17 +1812,23 @@
         <v>40</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
+        <v>122</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="18">
+        <v>46203</v>
+      </c>
+      <c r="H22" s="18">
+        <v>46206</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="10">
@@ -1808,39 +1838,51 @@
         <v>64</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+        <v>124</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="18">
+        <v>46206</v>
+      </c>
+      <c r="H23" s="18">
+        <v>46214</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" spans="1:8">
+        <v>126</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="18">
+        <v>46206</v>
+      </c>
+      <c r="H24" s="18">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="29">
       <c r="A25" s="10">
         <v>24</v>
       </c>
@@ -1848,34 +1890,36 @@
         <v>65</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+        <v>127</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="18">
+        <v>46206</v>
+      </c>
+      <c r="H25" s="18">
+        <v>46214</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>136</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
@@ -1885,17 +1929,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>140</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
@@ -1908,17 +1948,8 @@
         <v>46</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+        <v>131</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="10">
@@ -1928,19 +1959,10 @@
         <v>49</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" spans="1:8" ht="29">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -1948,17 +1970,8 @@
         <v>52</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
